--- a/analise_eua/tecnologia/amazon/amzn_10q.xlsx
+++ b/analise_eua/tecnologia/amazon/amzn_10q.xlsx
@@ -435,65 +435,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -504,60 +507,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>78213</v>
+      </c>
+      <c r="C2" t="n">
         <v>101816</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>66922</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>57741</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>66207</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>75091</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>71178</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>72852</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>49605</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>49529</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>49343</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>34947</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>37478</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>36393</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>29944</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>40380</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>33834</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>29930</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>37466</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>27201</v>
       </c>
     </row>
@@ -568,60 +574,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>44775</v>
+      </c>
+      <c r="C3" t="n">
         <v>41273</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>27275</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>35439</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>28358</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>12960</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>17914</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>12222</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>14564</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>14441</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>15062</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>23715</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>23232</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>29992</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>49044</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>49514</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>39436</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>38472</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>33925</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>22091</v>
       </c>
     </row>
@@ -632,60 +641,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>38184</v>
+      </c>
+      <c r="C4" t="n">
         <v>36534</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>41494</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>40825</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>35864</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>36103</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>34109</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>31147</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>35406</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>36587</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>34170</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>36647</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>38153</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>34987</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>30933</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>24119</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>23849</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>23735</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>19599</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>18857</v>
       </c>
     </row>
@@ -696,60 +708,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>88092</v>
+      </c>
+      <c r="C5" t="n">
         <v>75532</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>61175</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>57415</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>54216</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>51638</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>50106</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>47768</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>43420</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>39925</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>37646</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>36154</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>34804</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>32504</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>28610</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>26835</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>24289</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>20832</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>19918</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>17836</v>
       </c>
     </row>
@@ -760,60 +775,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>249264</v>
+      </c>
+      <c r="C6" t="n">
         <v>255155</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>196866</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>191420</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>184645</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>175792</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>173307</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>163989</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>142995</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>140482</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>136221</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>131463</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>133667</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>133876</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>138531</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>140848</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>121408</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>112969</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>110908</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>85985</v>
       </c>
     </row>
@@ -824,60 +842,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>446046</v>
+      </c>
+      <c r="C7" t="n">
         <v>397458</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>324435</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>297616</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>272781</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>237917</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>220717</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>209950</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>196468</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>193784</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>190754</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>177195</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>173706</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>168468</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>147152</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>133502</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>121461</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>99981</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>86517</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>77779</v>
       </c>
     </row>
@@ -888,60 +909,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>92743</v>
+      </c>
+      <c r="C8" t="n">
         <v>88741</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>83456</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>82125</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>78495</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>76527</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>74575</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>73313</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>70758</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>70332</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>68262</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>62033</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>58430</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>56161</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>52151</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>43346</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>39328</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>34119</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>28537</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>26279</v>
       </c>
     </row>
@@ -952,60 +976,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>23504</v>
+      </c>
+      <c r="C9" t="n">
         <v>23449</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>23260</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>23155</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>23089</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>23081</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>22879</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>22770</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>22749</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>22785</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>22749</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>20168</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>20195</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>20229</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>15345</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>15350</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>15220</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>14960</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>14751</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>14739</v>
       </c>
     </row>
@@ -1016,60 +1043,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>284132</v>
+      </c>
+      <c r="C10" t="n">
         <v>151827</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>99904</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>87854</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>84246</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>71309</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>63340</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>60947</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>53913</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>50224</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>46392</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>37503</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>33730</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>32033</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>29227</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>27273</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>25660</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>20150</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>17601</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>16456</v>
       </c>
     </row>
@@ -1080,60 +1110,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>1095689</v>
+      </c>
+      <c r="C11" t="n">
         <v>916630</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>727921</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>682170</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>643256</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>584626</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>554818</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>530969</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>486883</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>477607</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>464378</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>428362</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>419728</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>410767</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>382406</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>360319</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>323077</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>282179</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>258314</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>221238</v>
       </c>
     </row>
@@ -1144,60 +1177,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>147440</v>
+      </c>
+      <c r="C12" t="n">
         <v>124749</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>106032</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>98285</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>89241</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>84570</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>81817</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>73068</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>72004</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>69481</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>66907</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>67760</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>71219</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>68547</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>71474</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>66090</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>63926</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>58334</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>51036</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>40056</v>
       </c>
     </row>
@@ -1208,60 +1244,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>73406</v>
+      </c>
+      <c r="C13" t="n">
         <v>71120</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>68051</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>66974</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>66331</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>60602</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>60351</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>63970</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>58812</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>64235</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>66382</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>59974</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>56254</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>58141</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>41546</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>41007</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>40939</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>34327</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>33863</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>30791</v>
       </c>
     </row>
@@ -1272,60 +1311,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>20428</v>
+      </c>
+      <c r="C14" t="n">
         <v>20887</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>21113</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>21662</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>20599</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>16305</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>16004</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>15927</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>14398</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>14522</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>14281</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>12629</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>12818</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>12820</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>10974</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>10695</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>10539</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>9251</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>8997</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>8864</v>
       </c>
     </row>
@@ -1336,60 +1378,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>241274</v>
+      </c>
+      <c r="C15" t="n">
         <v>216756</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>195196</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>186921</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>176171</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>161477</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>158172</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>152965</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>145214</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>148238</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>147570</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>140363</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>140291</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>139508</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>123994</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>117792</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>115404</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>101912</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>93896</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>79711</v>
       </c>
     </row>
@@ -1400,60 +1445,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>94338</v>
+      </c>
+      <c r="C16" t="n">
         <v>90814</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>84677</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>83221</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>79871</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>79802</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>78084</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>77052</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>75891</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>75822</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>74267</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>69332</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>66524</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>65731</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>63848</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>56297</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>53067</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>48589</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>42798</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>40300</v>
       </c>
     </row>
@@ -1464,60 +1512,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>128894</v>
+      </c>
+      <c r="C17" t="n">
         <v>119074</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>50742</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>50718</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>53374</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>54890</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>54889</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>57634</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>61098</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>63092</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>67084</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>58919</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>58053</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>47556</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>50055</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>50279</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>31868</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>32929</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>33128</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>23437</v>
       </c>
     </row>
@@ -1528,60 +1579,63 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>79563</v>
+      </c>
+      <c r="C18" t="n">
         <v>48072</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>27675</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>27535</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>27973</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>29306</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>27226</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>26657</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>21707</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>21853</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>20931</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>22259</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>23458</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>23971</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>23945</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>21148</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>19418</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>15974</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>14764</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>12518</v>
       </c>
     </row>
@@ -1595,25 +1649,25 @@
         <v>113</v>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
         <v>112</v>
       </c>
       <c r="E19" t="n">
+        <v>112</v>
+      </c>
+      <c r="F19" t="n">
         <v>111</v>
-      </c>
-      <c r="F19" t="n">
-        <v>110</v>
       </c>
       <c r="G19" t="n">
         <v>110</v>
       </c>
       <c r="H19" t="n">
+        <v>110</v>
+      </c>
+      <c r="I19" t="n">
         <v>109</v>
-      </c>
-      <c r="I19" t="n">
-        <v>108</v>
       </c>
       <c r="J19" t="n">
         <v>108</v>
@@ -1622,13 +1676,13 @@
         <v>108</v>
       </c>
       <c r="L19" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M19" t="n">
         <v>107</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="O19" t="n">
         <v>5</v>
@@ -1648,6 +1702,9 @@
       <c r="T19" t="n">
         <v>5</v>
       </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1692,10 +1749,10 @@
         <v>-7837</v>
       </c>
       <c r="N20" t="n">
+        <v>-7837</v>
+      </c>
+      <c r="O20" t="n">
         <v>-4503</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-1837</v>
       </c>
       <c r="P20" t="n">
         <v>-1837</v>
@@ -1712,6 +1769,9 @@
       <c r="T20" t="n">
         <v>-1837</v>
       </c>
+      <c r="U20" t="n">
+        <v>-1837</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1720,60 +1780,63 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>149619</v>
+      </c>
+      <c r="C21" t="n">
         <v>143979</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>135679</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>130923</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>124514</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>115934</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>110633</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>103938</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>92711</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>86896</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>79863</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>69419</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>63871</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>58793</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>51879</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>48724</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>45160</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>40307</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>38017</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>35412</v>
       </c>
     </row>
@@ -1784,60 +1847,63 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>66287</v>
+      </c>
+      <c r="C22" t="n">
         <v>24868</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>12333</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>2420</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>-914</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>-1918</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-3993</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-3598</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-5003</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-3680</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-3973</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-7115</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>-4782</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-2365</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-1075</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>-525</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>-666</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>-1029</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-1455</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-2063</v>
       </c>
     </row>
@@ -1848,60 +1914,63 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>343438</v>
+      </c>
+      <c r="C23" t="n">
         <v>280791</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>229344</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>208157</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>189993</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>152862</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>137534</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>124049</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>102994</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>93115</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>86365</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>82915</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>80043</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>82071</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>71592</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>68436</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>60658</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>45329</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>38998</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>33755</v>
       </c>
     </row>
@@ -1912,60 +1981,63 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>551620</v>
+      </c>
+      <c r="C24" t="n">
         <v>441914</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>369631</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>333775</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>305867</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>259151</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>236447</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>216661</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>182973</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>168602</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>154526</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>137489</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>131402</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>134001</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>120564</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>114803</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>103320</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>82775</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>73728</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>65272</v>
       </c>
     </row>
@@ -1980,65 +2052,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -2049,60 +2124,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>200606</v>
+      </c>
+      <c r="C2" t="n">
         <v>181519</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>180169</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>167702</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>155667</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>158877</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>147977</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>143313</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>143083</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>134383</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>127358</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>127101</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>121234</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>116444</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>110812</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>113080</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>108518</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>96145</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>88912</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>75452</v>
       </c>
     </row>
@@ -2113,60 +2191,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>95778</v>
+      </c>
+      <c r="C3" t="n">
         <v>87463</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>88670</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>80809</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>76976</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>80977</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>73785</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>72633</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>75022</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>69373</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>67791</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>70268</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>66424</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>66499</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>62930</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>64176</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>62403</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>57106</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>52660</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>44257</v>
       </c>
     </row>
@@ -2177,60 +2258,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>29633</v>
+      </c>
+      <c r="C4" t="n">
         <v>27289</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>27679</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>25976</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>24593</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>24660</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>23566</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>22317</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>22314</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>21305</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>20905</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>20583</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>20342</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>20271</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>18498</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>17638</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>16530</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>14705</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>13806</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>11531</v>
       </c>
     </row>
@@ -2241,60 +2325,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>33158</v>
+      </c>
+      <c r="C5" t="n">
         <v>29567</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>28962</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>27166</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>22994</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>22245</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>22304</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>20424</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>21203</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>21931</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>20450</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>19485</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>18072</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>14842</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>14380</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>13871</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>12488</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>10976</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>10388</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>9325</v>
       </c>
     </row>
@@ -2305,60 +2392,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>11698</v>
+      </c>
+      <c r="C6" t="n">
         <v>10314</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>11686</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>11416</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>9763</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>10609</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>10512</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>9662</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>10551</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>10745</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>10172</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>11014</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>10086</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>8320</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>8010</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>7524</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>6207</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>5434</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>4345</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>4828</v>
       </c>
     </row>
@@ -2369,60 +2459,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2788</v>
+      </c>
+      <c r="C7" t="n">
         <v>2587</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>2875</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>2965</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2628</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2713</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>3041</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>2742</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2561</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>3202</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3043</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>3061</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2903</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2594</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>2153</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>2158</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>1987</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>1668</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1580</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1452</v>
       </c>
     </row>
@@ -2433,60 +2526,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" t="n">
         <v>447</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>2875</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>199</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>308</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>262</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>97</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>228</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>244</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>146</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>223</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>165</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>90</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>249</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-11</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>11</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>38</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>62</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>290</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>70</v>
       </c>
     </row>
@@ -2497,60 +2593,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>173145</v>
+      </c>
+      <c r="C9" t="n">
         <v>157667</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>162747</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>148531</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>137262</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>141466</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>133305</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>128006</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>131895</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>126702</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>122584</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>124576</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>117917</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>112775</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>105960</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>105378</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>99653</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>89951</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>83069</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>71463</v>
       </c>
     </row>
@@ -2561,60 +2660,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>27461</v>
+      </c>
+      <c r="C10" t="n">
         <v>23852</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>17422</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>19171</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>18405</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>17411</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>14672</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>15307</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>11188</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>7681</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4774</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2525</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>3317</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>3669</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>4852</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>7702</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>8865</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>6194</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>5843</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>3989</v>
       </c>
     </row>
@@ -2625,60 +2727,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>1295</v>
+      </c>
+      <c r="C11" t="n">
         <v>1135</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>1100</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>1085</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1066</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1256</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1180</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>993</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>776</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>661</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>611</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>277</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>159</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>108</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>119</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>106</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>105</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>118</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>135</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>202</v>
       </c>
     </row>
@@ -2689,60 +2794,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>1314</v>
+      </c>
+      <c r="C12" t="n">
         <v>800</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>538</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>516</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>541</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>603</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>589</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>644</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>806</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>840</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>823</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>617</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>584</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>472</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>493</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>435</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>399</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>428</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>403</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>402</v>
       </c>
     </row>
@@ -2753,60 +2861,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>53415</v>
+      </c>
+      <c r="C13" t="n">
         <v>15647</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>10186</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1117</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>2749</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-27</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-18</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-2673</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1031</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>61</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-443</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>759</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-5545</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-8570</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-163</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1261</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>1697</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>925</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>646</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-406</v>
       </c>
     </row>
@@ -2817,60 +2928,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>53396</v>
+      </c>
+      <c r="C14" t="n">
         <v>15982</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>10748</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1686</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>3274</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>626</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>573</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>-2324</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1001</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>-118</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>-655</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>419</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-5970</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>-8934</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>-537</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>932</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>1403</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>615</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>378</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-606</v>
       </c>
     </row>
@@ -2881,60 +2995,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>80857</v>
+      </c>
+      <c r="C15" t="n">
         <v>39834</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>28170</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>20857</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>21679</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>18037</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>15245</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>12983</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>12189</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>7563</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>4119</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2944</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>-2653</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>-5265</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>4315</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>8634</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>10268</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>6809</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>6221</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>3383</v>
       </c>
     </row>
@@ -2945,60 +3062,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>18199</v>
+      </c>
+      <c r="C16" t="n">
         <v>9560</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>6910</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>2678</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>4553</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>2706</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>1767</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>2467</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>2306</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>804</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>948</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>69</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>-637</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-1422</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1155</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>868</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>2156</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>569</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-984</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>744</v>
       </c>
     </row>
@@ -3009,60 +3129,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C17" t="n">
         <v>-19</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>-73</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>-15</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-3</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>7</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-85</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-9</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-3</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-12</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>-1</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-4</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>12</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>-5</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>91</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-104</v>
       </c>
     </row>
@@ -3073,60 +3196,63 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>62647</v>
+      </c>
+      <c r="C18" t="n">
         <v>30255</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>21187</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>18164</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>17127</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>15328</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>13485</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>10431</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>9879</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>6750</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>3172</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2872</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>-2028</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>-3844</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>3156</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>7778</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>8107</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>6331</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>5243</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>2535</v>
       </c>
     </row>
@@ -3137,60 +3263,63 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="C19" t="n">
         <v>2.82</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>1.98</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>1.71</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1.62</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>1.46</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1.29</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>0.96</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>0.66</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>0.31</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0.28</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>-7.56</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>6.23</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>15.4</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>16.09</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>12.63</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>10.5</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>5.09</v>
       </c>
     </row>
@@ -3201,60 +3330,63 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C20" t="n">
         <v>2.78</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>1.95</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>1.68</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>1.59</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>1.43</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>1.26</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0.98</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>0.65</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.28</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>-0.2</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>-7.56</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6.12</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>15.12</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15.79</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>12.37</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>10.3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>5.01</v>
       </c>
     </row>
@@ -3265,60 +3397,63 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>10769</v>
+      </c>
+      <c r="C21" t="n">
         <v>10743</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>10674</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>10637</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>10603</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>10501</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>10447</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>10393</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>10322</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>10285</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>10250</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>10191</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10175</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>509</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>507</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>505</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>504</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>501</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>500</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>498</v>
       </c>
     </row>
@@ -3329,60 +3464,63 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>10903</v>
+      </c>
+      <c r="C22" t="n">
         <v>10874</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>10845</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>10806</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>10793</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>10735</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>10708</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>10670</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10558</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>10449</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>10347</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>10331</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>10175</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>509</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>515</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>514</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>513</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>512</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>509</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>506</v>
       </c>
     </row>
@@ -3397,65 +3535,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -3466,60 +3607,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>104692</v>
+      </c>
+      <c r="C2" t="n">
         <v>90106</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>61453</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>69893</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>82312</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>71673</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>73332</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>73890</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>50067</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>49734</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>54253</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>37700</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>36599</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>36477</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>40667</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>34155</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>42377</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>37842</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>27505</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>36410</v>
       </c>
     </row>
@@ -3530,60 +3674,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>62647</v>
+      </c>
+      <c r="C3" t="n">
         <v>30255</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>21187</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>18164</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>17127</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>15328</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>13485</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>10431</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>9879</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>6750</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>3172</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>2872</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>-2028</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>-3844</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>3156</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>7778</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>8107</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>6331</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>5243</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>2535</v>
       </c>
     </row>
@@ -3594,60 +3741,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>19988</v>
+      </c>
+      <c r="C4" t="n">
         <v>18945</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>16796</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>15227</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>14262</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>13442</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>12038</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>11684</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>12131</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>11589</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>11123</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>10204</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>9594</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>8978</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>8948</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>8038</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>7508</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>6523</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>5748</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>5362</v>
       </c>
     </row>
@@ -3658,60 +3808,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>6038</v>
+      </c>
+      <c r="C5" t="n">
         <v>4032</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>4847</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>6534</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>3689</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>5333</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>6722</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4961</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5829</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>7127</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4748</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>5556</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>5209</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>3250</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3180</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3591</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2306</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>2288</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>2601</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1757</v>
       </c>
     </row>
@@ -3722,60 +3875,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-53381</v>
+      </c>
+      <c r="C6" t="n">
         <v>-15632</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-10112</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-1258</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-2817</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-141</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-95</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2734</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-990</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>47</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>534</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>-1272</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>6104</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>8689</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>340</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>-1258</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>-1456</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>-1051</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-769</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>565</v>
       </c>
     </row>
@@ -3786,60 +3942,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>17691</v>
+      </c>
+      <c r="C7" t="n">
         <v>12798</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>10130</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>11</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>507</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-1317</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-785</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-938</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>-1196</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-2744</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-472</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>-825</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>-1955</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-2001</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>909</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>701</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>1703</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>295</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>465</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>322</v>
       </c>
     </row>
@@ -3850,60 +4009,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>-1818</v>
+      </c>
+      <c r="C8" t="n">
         <v>1622</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>-827</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>-4054</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>-1222</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-1509</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>-3085</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1776</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>808</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>-2373</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>371</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>732</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>-3890</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>-2614</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-7059</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>-209</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>-304</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>-3899</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>-672</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1392</v>
       </c>
     </row>
@@ -3914,60 +4076,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-8204</v>
+      </c>
+      <c r="C9" t="n">
         <v>-5750</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-1977</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-1125</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1247</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-701</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-2209</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>3684</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-6718</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-5167</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>1521</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-4794</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-6799</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-1516</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>-4890</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>-4462</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-2255</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>-2016</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-2854</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>1262</v>
       </c>
     </row>
@@ -3978,37 +4143,37 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-4717</v>
+      </c>
+      <c r="C10" t="n">
         <v>-3811</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-4039</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-2971</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-3402</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-4537</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-3055</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-2701</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-3134</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-3126</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-3203</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -4034,6 +4199,9 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4042,60 +4210,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>9442</v>
+      </c>
+      <c r="C11" t="n">
         <v>-8737</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>2151</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>7058</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-9043</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-477</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>6005</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-11282</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>2820</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>3029</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-11264</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-1226</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>3699</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-9380</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>3832</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>47</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>-8266</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>3658</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>8616</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-8044</v>
       </c>
     </row>
@@ -4106,60 +4277,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-2018</v>
+      </c>
+      <c r="C12" t="n">
         <v>-8045</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>-1999</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-4952</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-4061</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>129</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-4147</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-2928</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-1321</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-1938</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-5763</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-20</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-1412</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>-5903</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>-1465</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>-1685</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>-4060</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>-310</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1699</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-2761</v>
       </c>
     </row>
@@ -4170,60 +4344,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-281</v>
+      </c>
+      <c r="C13" t="n">
         <v>355</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-632</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-119</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>728</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>421</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>407</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1568</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-25</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>156</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>818</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>54</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>321</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1336</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>338</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>156</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>900</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>78</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>247</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>607</v>
       </c>
     </row>
@@ -4234,60 +4411,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>45387</v>
+      </c>
+      <c r="C14" t="n">
         <v>26032</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>35525</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>32515</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>17015</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>25971</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>25281</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>18989</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>21217</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>16476</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4788</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>11404</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>8965</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>-2790</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>7313</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>12715</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>4213</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>11964</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>20606</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -4298,60 +4478,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>-54208</v>
+      </c>
+      <c r="C15" t="n">
         <v>-44203</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>-35095</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>-32183</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-25019</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-22620</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>-17620</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>-14925</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-12479</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-11455</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-14207</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>-16378</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>-15724</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>-14951</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>-15748</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>-14288</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>-12082</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>-11063</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-7459</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-6795</v>
       </c>
     </row>
@@ -4362,60 +4545,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>1132</v>
+      </c>
+      <c r="C16" t="n">
         <v>969</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>867</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>815</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>764</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>1342</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>1227</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>990</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>1181</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>1043</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1137</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>1337</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>1626</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>1209</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>997</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>1300</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>895</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>1255</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>844</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>1367</v>
       </c>
     </row>
@@ -4426,60 +4612,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>-24359</v>
+      </c>
+      <c r="C17" t="n">
         <v>-15408</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>-786</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>-1700</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>48</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-622</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-571</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-3354</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-1629</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-316</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-3513</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-885</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-259</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>-6341</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-654</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>-320</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>-630</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>-1735</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-118</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-91</v>
       </c>
     </row>
@@ -4490,60 +4679,63 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>24196</v>
+      </c>
+      <c r="C18" t="n">
         <v>17686</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>16367</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>11441</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>7737</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>8069</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>3265</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1392</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1393</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>1551</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1115</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>557</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>2608</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>22753</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>15808</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>13213</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>17826</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>13135</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>8138</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>11626</v>
       </c>
     </row>
@@ -4554,60 +4746,63 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>-26006</v>
+      </c>
+      <c r="C19" t="n">
         <v>-23256</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>-7426</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>-17797</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>-13333</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>-3068</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>-8439</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>-1965</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>-219</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>-496</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>-338</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>-239</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>-329</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>-1764</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>-15231</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>-21985</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>-14675</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>-17468</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>-19209</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>-15001</v>
       </c>
     </row>
@@ -4618,60 +4813,63 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>-79245</v>
+      </c>
+      <c r="C20" t="n">
         <v>-64212</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>-26073</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>-39424</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>-29803</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>-16899</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>-22138</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>-17862</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>-11753</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>-9673</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>-15806</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>-15608</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>-12078</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>906</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>-14828</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>-22080</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>-8666</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>-15876</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-17804</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-8894</v>
       </c>
     </row>
@@ -4682,60 +4880,63 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>9368</v>
+      </c>
+      <c r="C21" t="n">
         <v>6018</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>3223</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>2093</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>1815</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>1725</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>525</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>338</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>216</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>4399</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>12780</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>12338</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>4865</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>13743</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2187</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>1176</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>1926</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>1311</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>2433</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-667</v>
       </c>
     </row>
@@ -4746,60 +4947,63 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>-9573</v>
+      </c>
+      <c r="C22" t="n">
         <v>-6109</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>-1826</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>-1392</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>-2082</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>-1820</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-229</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-404</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-8095</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-7641</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-3603</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-7916</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>-7610</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-6231</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-1917</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>-1176</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>-2001</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>-1349</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-1906</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-631</v>
       </c>
     </row>
@@ -4810,19 +5014,19 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>13557</v>
+      </c>
+      <c r="C23" t="n">
         <v>53441</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>746</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4840,30 +5044,33 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>107</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>12824</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>176</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>18516</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>111</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>9918</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>693</v>
       </c>
     </row>
@@ -4874,60 +5081,63 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>-2752</v>
+      </c>
+      <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>-1008</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>-2751</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-2183</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-4169</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>-330</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-2000</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-1386</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>-1</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>-509</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>-41</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>-39</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>-1198</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-205</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-36</v>
       </c>
     </row>
@@ -4938,60 +5148,63 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>-395</v>
+      </c>
+      <c r="C25" t="n">
         <v>-468</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>-351</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>-411</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-410</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>-402</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>-538</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>-770</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>-1005</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-1220</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-1380</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-1465</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-2059</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>-2777</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>-2693</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>-2804</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>-3406</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>-2857</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-2817</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-2600</v>
       </c>
     </row>
@@ -5002,60 +5215,63 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>-59</v>
+      </c>
+      <c r="C26" t="n">
         <v>-115</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>-82</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>-78</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>-116</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>-78</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-79</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-90</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>-64</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>-77</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>-57</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>-48</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-59</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>-79</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>-20</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>-28</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>-67</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>-12</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>-15</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-17</v>
       </c>
     </row>
@@ -5066,60 +5282,63 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>10146</v>
+      </c>
+      <c r="C27" t="n">
         <v>52767</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>-44</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>-2539</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>-47</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>-2758</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>-4490</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>-1256</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>-8948</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>-6539</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>6354</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>3016</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>4626</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>1990</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>-2776</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>15643</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>-3476</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>-4105</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>7408</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>-2591</v>
       </c>
     </row>
@@ -5130,60 +5349,63 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>-53</v>
+      </c>
+      <c r="C28" t="n">
         <v>-1</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>-397</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>1008</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>416</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>690</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>-312</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>-429</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>-502</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>69</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>145</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>-1334</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>-412</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>16</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>-199</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>234</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>-293</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>377</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>127</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-484</v>
       </c>
     </row>
@@ -5194,60 +5416,63 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>-23765</v>
+      </c>
+      <c r="C29" t="n">
         <v>14586</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>9011</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>-8440</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>-12419</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>7004</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>-1659</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>-558</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>14</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>333</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>-4519</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>-2522</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>1101</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>122</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>-10490</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>6512</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>-8222</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>-7640</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10337</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>-8905</v>
       </c>
     </row>
@@ -5291,13 +5516,13 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>-3334</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>-2666</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -5314,6 +5539,9 @@
       <c r="T30" t="n">
         <v>0</v>
       </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5352,30 +5580,33 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>123</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>122</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>215</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>24</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>18</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>30</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>67</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>282</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>67</v>
       </c>
     </row>
@@ -5390,65 +5621,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -5459,60 +5693,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>15433</v>
+      </c>
+      <c r="C2" t="n">
         <v>14128</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>13321</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>12973</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>12243</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>10694</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>10175</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>10207</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>10477</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>11006</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>11428</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>12082</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>12499</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>13482</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>14625</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>14656</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>14703</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>14416</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>13591</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>13103</v>
       </c>
     </row>
@@ -5527,65 +5764,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -5596,60 +5836,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>3330</v>
+      </c>
+      <c r="C2" t="n">
         <v>2.832</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>3997</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>5005</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>5014</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>5248</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>7429</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>8848</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5995</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>3997</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>2000</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>4247</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>4998</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2681</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1000</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>1158</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>1156</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>155</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>1154</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1311</v>
       </c>
     </row>
